--- a/Bases_de_Dados/FootyStats/Denmark Superliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Denmark Superliga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP127"/>
+  <dimension ref="A1:BP133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.45</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.27</v>
@@ -3094,7 +3094,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.18</v>
@@ -3527,7 +3527,7 @@
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.45</v>
@@ -3745,10 +3745,10 @@
         <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR15" t="n">
         <v>1.52</v>
@@ -3963,10 +3963,10 @@
         <v>3</v>
       </c>
       <c r="AP16" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR16" t="n">
         <v>1.27</v>
@@ -4184,7 +4184,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4835,10 +4835,10 @@
         <v>1</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR20" t="n">
         <v>1.53</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.18</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.18</v>
@@ -5492,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR23" t="n">
         <v>1.89</v>
@@ -5928,7 +5928,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR25" t="n">
         <v>1.51</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.18</v>
@@ -6579,7 +6579,7 @@
         <v>1</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.91</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR29" t="n">
         <v>1.01</v>
@@ -7018,7 +7018,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR30" t="n">
         <v>1.23</v>
@@ -7236,7 +7236,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ31" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR31" t="n">
         <v>1.25</v>
@@ -7451,10 +7451,10 @@
         <v>0.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR32" t="n">
         <v>1.82</v>
@@ -7669,10 +7669,10 @@
         <v>1</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR33" t="n">
         <v>2.06</v>
@@ -7887,10 +7887,10 @@
         <v>1.33</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR34" t="n">
         <v>1.46</v>
@@ -8105,10 +8105,10 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR35" t="n">
         <v>1.03</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.27</v>
@@ -9416,7 +9416,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR41" t="n">
         <v>1.4</v>
@@ -10067,10 +10067,10 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR44" t="n">
         <v>1.02</v>
@@ -10503,10 +10503,10 @@
         <v>2.33</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR46" t="n">
         <v>1.19</v>
@@ -10942,7 +10942,7 @@
         <v>1</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR48" t="n">
         <v>1.75</v>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.27</v>
@@ -11593,7 +11593,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.27</v>
@@ -11811,7 +11811,7 @@
         <v>0.75</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.18</v>
@@ -12029,10 +12029,10 @@
         <v>0.75</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR53" t="n">
         <v>1.84</v>
@@ -12250,7 +12250,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR54" t="n">
         <v>2.17</v>
@@ -12468,7 +12468,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR55" t="n">
         <v>1.13</v>
@@ -12683,7 +12683,7 @@
         <v>2.4</v>
       </c>
       <c r="AP56" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.45</v>
@@ -12901,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.18</v>
@@ -13340,7 +13340,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ59" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR59" t="n">
         <v>1.56</v>
@@ -13558,7 +13558,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR60" t="n">
         <v>1.68</v>
@@ -13773,10 +13773,10 @@
         <v>1.4</v>
       </c>
       <c r="AP61" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR61" t="n">
         <v>2.15</v>
@@ -14427,10 +14427,10 @@
         <v>1.2</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR64" t="n">
         <v>1.39</v>
@@ -14648,7 +14648,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR65" t="n">
         <v>2.05</v>
@@ -14863,7 +14863,7 @@
         <v>1.75</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.91</v>
@@ -15081,10 +15081,10 @@
         <v>1.5</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR67" t="n">
         <v>1.4</v>
@@ -15520,7 +15520,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR69" t="n">
         <v>1.52</v>
@@ -15735,10 +15735,10 @@
         <v>0.4</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR70" t="n">
         <v>1.35</v>
@@ -15956,7 +15956,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ71" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR71" t="n">
         <v>1.7</v>
@@ -16171,7 +16171,7 @@
         <v>0.4</v>
       </c>
       <c r="AP72" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.27</v>
@@ -16389,7 +16389,7 @@
         <v>0.8</v>
       </c>
       <c r="AP73" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.18</v>
@@ -16610,7 +16610,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR74" t="n">
         <v>2.13</v>
@@ -16825,7 +16825,7 @@
         <v>1.6</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.91</v>
@@ -17043,10 +17043,10 @@
         <v>0.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR76" t="n">
         <v>1.38</v>
@@ -17479,7 +17479,7 @@
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.27</v>
@@ -17700,7 +17700,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR79" t="n">
         <v>1.39</v>
@@ -17915,7 +17915,7 @@
         <v>0.67</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.18</v>
@@ -18133,10 +18133,10 @@
         <v>1</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR81" t="n">
         <v>1.28</v>
@@ -18351,7 +18351,7 @@
         <v>0.33</v>
       </c>
       <c r="AP82" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.27</v>
@@ -18572,7 +18572,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR83" t="n">
         <v>1.52</v>
@@ -18790,7 +18790,7 @@
         <v>1</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR84" t="n">
         <v>1.36</v>
@@ -19005,10 +19005,10 @@
         <v>2.33</v>
       </c>
       <c r="AP85" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ85" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR85" t="n">
         <v>2.05</v>
@@ -19226,7 +19226,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR86" t="n">
         <v>1.41</v>
@@ -19441,7 +19441,7 @@
         <v>2.14</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.45</v>
@@ -19659,7 +19659,7 @@
         <v>1</v>
       </c>
       <c r="AP88" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.27</v>
@@ -20316,7 +20316,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR91" t="n">
         <v>1.64</v>
@@ -20534,7 +20534,7 @@
         <v>1</v>
       </c>
       <c r="AQ92" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR92" t="n">
         <v>1.4</v>
@@ -20749,10 +20749,10 @@
         <v>2.14</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR93" t="n">
         <v>1.86</v>
@@ -20967,7 +20967,7 @@
         <v>0.29</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.27</v>
@@ -21403,7 +21403,7 @@
         <v>2</v>
       </c>
       <c r="AP96" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.91</v>
@@ -21624,7 +21624,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR97" t="n">
         <v>1.32</v>
@@ -21839,7 +21839,7 @@
         <v>1.25</v>
       </c>
       <c r="AP98" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.27</v>
@@ -22060,7 +22060,7 @@
         <v>1</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR99" t="n">
         <v>1.42</v>
@@ -22493,10 +22493,10 @@
         <v>1.13</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR101" t="n">
         <v>2</v>
@@ -23147,10 +23147,10 @@
         <v>1.13</v>
       </c>
       <c r="AP104" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR104" t="n">
         <v>1.29</v>
@@ -23368,7 +23368,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR105" t="n">
         <v>1.81</v>
@@ -23583,7 +23583,7 @@
         <v>1.75</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.91</v>
@@ -23804,7 +23804,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ107" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR107" t="n">
         <v>1.36</v>
@@ -24019,7 +24019,7 @@
         <v>1.13</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.18</v>
@@ -24237,10 +24237,10 @@
         <v>1.88</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR109" t="n">
         <v>1.39</v>
@@ -24891,7 +24891,7 @@
         <v>1.67</v>
       </c>
       <c r="AP112" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.45</v>
@@ -25112,7 +25112,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR113" t="n">
         <v>1.73</v>
@@ -25327,7 +25327,7 @@
         <v>0.78</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.18</v>
@@ -25548,7 +25548,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR115" t="n">
         <v>2.11</v>
@@ -25981,10 +25981,10 @@
         <v>1</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR117" t="n">
         <v>1.88</v>
@@ -26199,10 +26199,10 @@
         <v>2.33</v>
       </c>
       <c r="AP118" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ118" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR118" t="n">
         <v>1.28</v>
@@ -26635,10 +26635,10 @@
         <v>1.67</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR120" t="n">
         <v>1.22</v>
@@ -26853,10 +26853,10 @@
         <v>0.89</v>
       </c>
       <c r="AP121" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR121" t="n">
         <v>1.43</v>
@@ -28240,6 +28240,1314 @@
       </c>
       <c r="BP127" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="n">
+        <v>7963620</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Denmark Superliga</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F128" t="n">
+        <v>22</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Viborg</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Nordsjælland</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" t="n">
+        <v>2</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1</v>
+      </c>
+      <c r="N128" t="n">
+        <v>3</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>['8', '72']</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R128" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S128" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T128" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U128" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V128" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W128" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X128" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="n">
+        <v>7963581</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Denmark Superliga</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F129" t="n">
+        <v>22</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>SønderjyskE</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R129" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S129" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T129" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U129" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V129" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W129" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X129" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="n">
+        <v>7963567</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Denmark Superliga</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F130" t="n">
+        <v>22</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>København</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Randers</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="n">
+        <v>2</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" t="n">
+        <v>2</v>
+      </c>
+      <c r="N130" t="n">
+        <v>3</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>['17', '90+12']</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R130" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U130" t="n">
+        <v>3</v>
+      </c>
+      <c r="V130" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="W130" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X130" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="n">
+        <v>7963616</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Denmark Superliga</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F131" t="n">
+        <v>22</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Vejle</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" t="n">
+        <v>2</v>
+      </c>
+      <c r="N131" t="n">
+        <v>3</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>['46', '71']</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>5</v>
+      </c>
+      <c r="R131" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S131" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T131" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U131" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="V131" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W131" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X131" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="n">
+        <v>7963580</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Denmark Superliga</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F132" t="n">
+        <v>22</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Fredericia</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Silkeborg</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="n">
+        <v>2</v>
+      </c>
+      <c r="L132" t="n">
+        <v>2</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" t="n">
+        <v>3</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>['45+1', '68']</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R132" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S132" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T132" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U132" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V132" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="W132" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X132" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="n">
+        <v>7963568</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Denmark Superliga</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F133" t="n">
+        <v>22</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Midtjylland</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Brøndby</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>2</v>
+      </c>
+      <c r="R133" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U133" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V133" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X133" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Denmark Superliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Denmark Superliga_20252026.xlsx
@@ -28618,13 +28618,13 @@
         <v>2</v>
       </c>
       <c r="AW129" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX129" t="n">
         <v>11</v>
       </c>
       <c r="AY129" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ129" t="n">
         <v>13</v>

--- a/Bases_de_Dados/FootyStats/Denmark Superliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Denmark Superliga_20252026.xlsx
@@ -28394,7 +28394,7 @@
         <v>2.64</v>
       </c>
       <c r="AU128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV128" t="n">
         <v>4</v>
@@ -28406,7 +28406,7 @@
         <v>11</v>
       </c>
       <c r="AY128" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ128" t="n">
         <v>15</v>
